--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -6940,7 +6940,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Détecter</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="C183" t="n">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -9700,7 +9700,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Détecter</t>
+          <t>Protéger</t>
         </is>
       </c>
       <c r="C260" t="n">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Protéger</t>
+          <t>Gouverner</t>
         </is>
       </c>
       <c r="C42" t="n">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H297"/>
+  <dimension ref="A1:H298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11056,6 +11056,34 @@
         </is>
       </c>
     </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Nucleon Security (Nucleon EDR)</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Protéger</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>3</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Nucleon Security (Nucleon EDR)_01.svg</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H298"/>
+  <dimension ref="A1:H299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11076,13 +11076,37 @@
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Nucleon Security (CyclonShield MDR)</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Détecter</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>3</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Nucleon Security (CyclonShield MDR)_01.svg</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H299"/>
+  <dimension ref="A1:H300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11100,13 +11100,37 @@
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="F299" t="inlineStr"/>
       <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Nucleon Security (Nucleon Malprob)</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Répondre</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>3</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Nucleon Security (Nucleon Malprob)_01.svg</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H300"/>
+  <dimension ref="A1:H301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11124,13 +11124,37 @@
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="F300" t="inlineStr"/>
       <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Sharekey</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Protéger</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>3</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Sharekey_01.png</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -4356,7 +4356,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Protéger</t>
+          <t>Détecter</t>
         </is>
       </c>
       <c r="C110" t="n">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -9268,7 +9268,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Détecter</t>
         </is>
       </c>
       <c r="C248" t="n">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H300"/>
+  <dimension ref="A1:H301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11116,6 +11116,34 @@
       <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr"/>
     </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>TrustBuilder</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Protéger</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>2</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>TrustBuilder_01.png</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H301"/>
+  <dimension ref="A1:H302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11136,13 +11136,41 @@
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Cyberdetect</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Détecter</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>3</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Cyberdetect_01.png</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>DE.CM, DE.AE</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H302"/>
+  <dimension ref="A1:H303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11164,13 +11164,41 @@
           <t>DE.CM, DE.AE</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Ercom</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Protéger</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>2</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Ercom_01.png</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>PR.IR</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
@@ -11192,11 +11192,7 @@
           <t>PR.IR</t>
         </is>
       </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="F303" t="inlineStr"/>
       <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr"/>
     </row>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -2733,7 +2733,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Gouverner</t>
         </is>
       </c>
       <c r="C65" t="n">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -4712,11 +4712,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Détecter</t>
+          <t>Récupérer</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -8368,11 +8368,11 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Détecter</t>
+          <t>Protéger</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H303"/>
+  <dimension ref="A1:H304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11196,6 +11196,38 @@
       <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr"/>
     </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>AFNIC</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Protéger</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>2</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>AFNIC_01.svg</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>PR.AA</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -10776,7 +10776,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Détecter</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -11220,11 +11220,7 @@
           <t>PR.AA</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr"/>
     </row>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -8944,7 +8944,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Répondre</t>
+          <t>Protéger</t>
         </is>
       </c>
       <c r="C239" t="n">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -8476,7 +8476,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Répondre</t>
+          <t>Détecter</t>
         </is>
       </c>
       <c r="C226" t="n">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -9992,7 +9992,7 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -9308,7 +9308,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H304"/>
+  <dimension ref="A1:H305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11224,6 +11224,34 @@
       <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr"/>
     </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>N-CYP</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Détecter</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>2</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>N-CYP_01.png</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H305"/>
+  <dimension ref="A1:H306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11244,13 +11244,41 @@
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="F305" t="inlineStr"/>
       <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Suricate</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Protéger</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>3</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Suricate_01.png</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>PR.PS</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H306"/>
+  <dimension ref="A1:H307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11272,13 +11272,41 @@
           <t>PR.PS</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="F306" t="inlineStr"/>
       <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Nucleon Security</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Protéger</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>3</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Nucleon Security_01.png</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>PR.PS</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H307"/>
+  <dimension ref="A1:H308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11300,13 +11300,41 @@
           <t>PR.PS</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="F307" t="inlineStr"/>
       <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>ERIUM</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Répondre</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>2</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>ERIUM_01.png</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>RS.MA</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -2805,7 +2805,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Détecter</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -11328,11 +11328,7 @@
           <t>RS.MA</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr"/>
     </row>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -11100,7 +11100,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Cyberdetect_01.png</t>
+          <t>Cyberdetect_02.png</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -2196,7 +2196,11 @@
       <c r="C50" t="n">
         <v>3</v>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Cloud IAM_02.png</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>PR.AA</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -11104,7 +11104,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Cyberdetect_02.png</t>
+          <t>Cyberdetect_03.png</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -11104,7 +11104,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Cyberdetect_03.png</t>
+          <t>Cyberdetect_04.png</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -11100,7 +11100,7 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -10860,7 +10860,7 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -8880,7 +8880,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -6600,7 +6600,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -6350,7 +6350,11 @@
       <c r="C166" t="n">
         <v>2</v>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>OGO Security_02.png</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>PR.PS, DE.CM, DE.AE</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -880,7 +880,11 @@
       <c r="C13" t="n">
         <v>0</v>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AntemetA_01.svg</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>PR.DS, PR.IR</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -1352,7 +1352,11 @@
       <c r="C26" t="n">
         <v>2</v>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Avant de Cliquer_01.png</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>PR.AT, DE.CM</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -1968,7 +1968,11 @@
       <c r="C43" t="n">
         <v>3</v>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CartographIT_01.png</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>GV.OC, ID.AM, ID.RA, ID.IM</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -2184,7 +2184,11 @@
       <c r="C49" t="n">
         <v>1</v>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Clever Cloud_01.svg</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>PR.DS, PR.PS</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -520,7 +520,11 @@
       <c r="C3" t="n">
         <v>3</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AAIS Armageddon AI Security (AAIS.ai)_01.png</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>DE.AE, DE.CM, RS.MA, RS.AN, PR.DS</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -2580,7 +2580,11 @@
       <c r="C60" t="n">
         <v>3</v>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Cryptr_01.png</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>PR.AA</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -3055,7 +3055,11 @@
       <c r="C73" t="n">
         <v>3</v>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Datasure_01.png</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>PR.DS, PR.AA</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -5883,7 +5883,11 @@
       <c r="C152" t="n">
         <v>3</v>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>MOABI SOLUTIONS_02.png</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>ID.RA, GV.SC, ID.IM</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -6029,7 +6029,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -7454,7 +7454,11 @@
       <c r="C196" t="n">
         <v>3</v>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Purplemet_02.png</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>ID.AM, DE.CM</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -7602,7 +7602,11 @@
       <c r="C200" t="n">
         <v>3</v>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Ravel Technologies_01.jpg</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>PR.DS, PR.PS</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -8206,7 +8206,11 @@
       <c r="C217" t="n">
         <v>3</v>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>SecDojo_01.png</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>PR.AT, RS.MI</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -9792,7 +9792,7 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -10118,7 +10118,11 @@
       <c r="C270" t="n">
         <v>3</v>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Uncovery_02.png</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>DE.CM, DE.AE, PR.PS</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -10590,7 +10590,11 @@
       <c r="C283" t="n">
         <v>3</v>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Woleet_02.png</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>PR.DS, DE.CM</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -11026,7 +11026,11 @@
       <c r="C295" t="n">
         <v>2</v>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Ziwit_01.jpg</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>DE.CM, DE.AE, PR.PS, PR.DS</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -11188,7 +11188,7 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H306"/>
+  <dimension ref="A1:H307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11340,6 +11340,34 @@
       <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr"/>
     </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Cogiceo</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>2</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Cogiceo_01.png</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr"/>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -4852,7 +4852,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Répondre</t>
+          <t>Détecter</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -11360,11 +11360,7 @@
         </is>
       </c>
       <c r="E307" t="inlineStr"/>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="F307" t="inlineStr"/>
       <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr"/>
     </row>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -7022,7 +7022,11 @@
       <c r="C184" t="n">
         <v>3</v>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>PORTYQ_01.svg</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>DE.CM, DE.AE</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -4322,7 +4322,11 @@
       <c r="C108" t="n">
         <v>3</v>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>GottaPhish_02.png</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>PR.AT</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -2360,7 +2360,11 @@
       <c r="C54" t="n">
         <v>3</v>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Continus.io_02.png</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>ID.RA, PR.PS</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -2879,7 +2879,11 @@
       <c r="C68" t="n">
         <v>3</v>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CyferAll (Qrshield)_01.webp</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>PR.DS, PR.PT</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -6650,7 +6650,11 @@
       <c r="C173" t="n">
         <v>3</v>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>OpenSezam (AuthSezam)_01.png</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>PR.AA, ID.AM</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cloud IAM_02.png</t>
+          <t>Cloud IAM_03.png</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -9166,7 +9166,11 @@
       <c r="C243" t="n">
         <v>2</v>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>SYLink Technologie_02.webp</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>GV.RM, GV.OV, DE.CM, DE.AE</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -10870,7 +10870,11 @@
       <c r="C290" t="n">
         <v>3</v>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Yneos (Malva.RE)_01.png</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>DE.CM, DE.AE</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -6894,7 +6894,11 @@
       <c r="C180" t="n">
         <v>3</v>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Parcoor_02.png</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>DE.CM, PR.PT</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -6115,7 +6115,11 @@
       <c r="C158" t="n">
         <v>3</v>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Neowave_02.png</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>PR.AA, PR.PS, PR.DS</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -9250,7 +9250,11 @@
       <c r="C245" t="n">
         <v>2</v>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Syspertec Group_02.png</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>PR.PS, PR.DS, DE.CM</t>

--- a/assets/solutions.xlsx
+++ b/assets/solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H301"/>
+  <dimension ref="A1:H302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11212,6 +11212,34 @@
       <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr"/>
     </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>PushManager</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>1</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>PushManager_01.png</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
